--- a/auto processes mappings.xlsx
+++ b/auto processes mappings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dessy\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavlo\Documents\Dev Projects\Python-Projects\SpotiCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200D37F0-4D48-4DD9-A6B4-4048368C4310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E48EA1C-306F-4752-9A7E-28F9806F86DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E6F67748-02B5-4CF8-9926-27FD300CD4B1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E6F67748-02B5-4CF8-9926-27FD300CD4B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Auto Processes" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="112">
   <si>
     <t>Action</t>
   </si>
@@ -281,9 +281,6 @@
   </si>
   <si>
     <t>Check</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
   <si>
     <t>albums_links &gt; album_id</t>
@@ -426,115 +423,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <strike val="0"/>
@@ -848,62 +737,62 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{532475EA-17EE-477E-9D25-56211A358147}" name="Table3" displayName="Table3" ref="A1:A4" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{532475EA-17EE-477E-9D25-56211A358147}" name="Table3" displayName="Table3" ref="A1:A4" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="A1:A4" xr:uid="{532475EA-17EE-477E-9D25-56211A358147}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{40FFB630-7477-4A66-8A57-3C450F77E1CB}" name="Actions" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{40FFB630-7477-4A66-8A57-3C450F77E1CB}" name="Actions" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CE5ED0D7-7266-4D8A-98E5-AA9873355450}" name="Table35" displayName="Table35" ref="C1:C4" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{CE5ED0D7-7266-4D8A-98E5-AA9873355450}" name="Table35" displayName="Table35" ref="C1:C4" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="C1:C4" xr:uid="{CE5ED0D7-7266-4D8A-98E5-AA9873355450}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{A8368D89-2255-42EC-A691-17F662B1A7A3}" name="Changes" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{A8368D89-2255-42EC-A691-17F662B1A7A3}" name="Changes" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{984BF581-A684-49BB-825A-E29A3127DA95}" name="Table36" displayName="Table36" ref="E1:E6" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{984BF581-A684-49BB-825A-E29A3127DA95}" name="Table36" displayName="Table36" ref="E1:E6" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
   <autoFilter ref="E1:E6" xr:uid="{984BF581-A684-49BB-825A-E29A3127DA95}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{0DE6F45A-F779-45F1-9DC9-F6703ADEA07E}" name="Triggers" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{0DE6F45A-F779-45F1-9DC9-F6703ADEA07E}" name="Triggers" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{E35F6ADE-D851-4ABA-8EA1-F11B842BC4D2}" name="Table37" displayName="Table37" ref="G1:G6" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{E35F6ADE-D851-4ABA-8EA1-F11B842BC4D2}" name="Table37" displayName="Table37" ref="G1:G6" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
   <autoFilter ref="G1:G6" xr:uid="{E35F6ADE-D851-4ABA-8EA1-F11B842BC4D2}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{FB805A57-C107-47D2-B226-F19C54CE2532}" name="Functions" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{FB805A57-C107-47D2-B226-F19C54CE2532}" name="Functions" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{4E45FB73-F7E0-40DD-9DF3-677B30C094F7}" name="Table38" displayName="Table38" ref="I1:I8" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{4E45FB73-F7E0-40DD-9DF3-677B30C094F7}" name="Table38" displayName="Table38" ref="I1:I8" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
   <autoFilter ref="I1:I8" xr:uid="{4E45FB73-F7E0-40DD-9DF3-677B30C094F7}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{CD50D8DA-7285-4961-ABDC-6637F618B6DB}" name="Views" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{CD50D8DA-7285-4961-ABDC-6637F618B6DB}" name="Views" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{B06AD1B3-B143-4B43-852C-39F5086D3CF4}" name="Table39" displayName="Table39" ref="K1:M47" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{B06AD1B3-B143-4B43-852C-39F5086D3CF4}" name="Table39" displayName="Table39" ref="K1:M47" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="K1:M47" xr:uid="{B06AD1B3-B143-4B43-852C-39F5086D3CF4}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EF2F403E-30AC-406C-A7E9-3126F5227A99}" name="Tables" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{FEFD2424-2EC7-4125-90A7-3F077F21D091}" name="Columns" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{3131D213-AED3-4040-BF70-534E82EA861B}" name="Lookup" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{EF2F403E-30AC-406C-A7E9-3126F5227A99}" name="Tables" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{FEFD2424-2EC7-4125-90A7-3F077F21D091}" name="Columns" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{3131D213-AED3-4040-BF70-534E82EA861B}" name="Lookup" dataDxfId="0">
       <calculatedColumnFormula>_xlfn.CONCAT(Table39[[#This Row],[Tables]], " &gt; ", Table39[[#This Row],[Columns]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -911,30 +800,10 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{95116BE1-D155-4CF8-86EA-9B12018F83F1}" name="Table2" displayName="Table2" ref="O1:O3" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="O1:O3" xr:uid="{95116BE1-D155-4CF8-86EA-9B12018F83F1}"/>
-  <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{096F24AF-8601-4AEA-8581-26D65F272DCC}" name="Check" dataDxfId="3"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{ED3A1910-DB84-4972-B6D5-D8BAB0C5D98B}" name="Table9" displayName="Table9" ref="Q1:Q3" totalsRowShown="0" headerRowDxfId="2" dataDxfId="1">
-  <autoFilter ref="Q1:Q3" xr:uid="{ED3A1910-DB84-4972-B6D5-D8BAB0C5D98B}"/>
-  <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{9B8176EE-8318-4953-99EB-3268A6AB6B62}" name="Values" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -972,7 +841,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1078,7 +947,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1220,7 +1089,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1229,20 +1098,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F817A46B-D7C4-49BB-A80E-20E00E62A9C6}">
   <dimension ref="A1:I57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1256,7 +1125,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F1" t="s">
         <v>9</v>
@@ -1271,7 +1140,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1285,24 +1154,24 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1311,24 +1180,24 @@
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1337,24 +1206,24 @@
         <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1363,19 +1232,19 @@
         <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1389,24 +1258,24 @@
         <v>7</v>
       </c>
       <c r="E6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
         <v>28</v>
@@ -1415,24 +1284,24 @@
         <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
         <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
         <v>28</v>
@@ -1441,24 +1310,24 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" t="s">
         <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
@@ -1467,24 +1336,24 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
@@ -1493,24 +1362,24 @@
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F10" t="s">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
         <v>28</v>
@@ -1519,24 +1388,24 @@
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F11" t="s">
         <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
@@ -1545,24 +1414,24 @@
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
       </c>
       <c r="G12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H12" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
@@ -1571,24 +1440,24 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
@@ -1597,24 +1466,24 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
       </c>
       <c r="G14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
         <v>26</v>
@@ -1623,24 +1492,24 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
@@ -1649,24 +1518,24 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
         <v>17</v>
       </c>
       <c r="G16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H16" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
         <v>26</v>
@@ -1675,24 +1544,24 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F17" t="s">
         <v>17</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
         <v>26</v>
@@ -1701,24 +1570,24 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
       </c>
       <c r="G18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
         <v>26</v>
@@ -1727,24 +1596,24 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H19" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
         <v>26</v>
@@ -1753,24 +1622,24 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F20" t="s">
         <v>16</v>
       </c>
       <c r="G20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H20" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
@@ -1779,24 +1648,24 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s">
         <v>16</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H21" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
         <v>26</v>
@@ -1805,24 +1674,24 @@
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
       </c>
       <c r="G22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H22" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
@@ -1831,24 +1700,24 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F23" t="s">
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H23" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -1857,24 +1726,24 @@
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
       </c>
       <c r="G24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H24" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
         <v>26</v>
@@ -1883,24 +1752,24 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
         <v>17</v>
       </c>
       <c r="G25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
         <v>26</v>
@@ -1909,24 +1778,24 @@
         <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F26" t="s">
         <v>17</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
         <v>26</v>
@@ -1935,24 +1804,24 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F27" t="s">
         <v>17</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s">
         <v>26</v>
@@ -1961,24 +1830,24 @@
         <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F28" t="s">
         <v>16</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H28" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>15</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
         <v>26</v>
@@ -1987,24 +1856,24 @@
         <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
         <v>16</v>
       </c>
       <c r="G29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H29" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
         <v>26</v>
@@ -2013,24 +1882,24 @@
         <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F30" t="s">
         <v>16</v>
       </c>
       <c r="G30" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H30" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
         <v>26</v>
@@ -2039,24 +1908,24 @@
         <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F31" t="s">
         <v>16</v>
       </c>
       <c r="G31" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H31" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C32" t="s">
         <v>26</v>
@@ -2065,24 +1934,24 @@
         <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F32" t="s">
         <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H32" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
         <v>26</v>
@@ -2091,24 +1960,24 @@
         <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s">
         <v>17</v>
       </c>
       <c r="G33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H33" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>8</v>
       </c>
       <c r="B34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
@@ -2117,24 +1986,24 @@
         <v>23</v>
       </c>
       <c r="E34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F34" t="s">
         <v>17</v>
       </c>
       <c r="G34" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H34" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>8</v>
       </c>
       <c r="B35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
@@ -2143,24 +2012,24 @@
         <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F35" t="s">
         <v>17</v>
       </c>
       <c r="G35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H35" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>8</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s">
         <v>27</v>
@@ -2169,24 +2038,24 @@
         <v>23</v>
       </c>
       <c r="E36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F36" t="s">
         <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H36" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>8</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
         <v>27</v>
@@ -2195,24 +2064,24 @@
         <v>23</v>
       </c>
       <c r="E37" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F37" t="s">
         <v>16</v>
       </c>
       <c r="G37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H37" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>14</v>
       </c>
       <c r="B38" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
@@ -2221,24 +2090,24 @@
         <v>23</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F38" t="s">
         <v>17</v>
       </c>
       <c r="G38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H38" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
         <v>27</v>
@@ -2247,24 +2116,24 @@
         <v>23</v>
       </c>
       <c r="E39" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F39" t="s">
         <v>17</v>
       </c>
       <c r="G39" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H39" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
@@ -2273,24 +2142,24 @@
         <v>23</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F40" t="s">
         <v>17</v>
       </c>
       <c r="G40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H40" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
@@ -2299,24 +2168,24 @@
         <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
         <v>16</v>
       </c>
       <c r="G41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
         <v>27</v>
@@ -2325,24 +2194,24 @@
         <v>23</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F42" t="s">
         <v>16</v>
       </c>
       <c r="G42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H42" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C43" t="s">
         <v>27</v>
@@ -2351,24 +2220,24 @@
         <v>23</v>
       </c>
       <c r="E43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F43" t="s">
         <v>16</v>
       </c>
       <c r="G43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H43" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>8</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C44" t="s">
         <v>29</v>
@@ -2377,24 +2246,24 @@
         <v>25</v>
       </c>
       <c r="E44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F44" t="s">
         <v>16</v>
       </c>
       <c r="G44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H44" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>8</v>
       </c>
       <c r="B45" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
         <v>29</v>
@@ -2403,24 +2272,24 @@
         <v>25</v>
       </c>
       <c r="E45" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F45" t="s">
         <v>16</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H45" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>8</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C46" t="s">
         <v>29</v>
@@ -2429,24 +2298,24 @@
         <v>25</v>
       </c>
       <c r="E46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F46" t="s">
         <v>16</v>
       </c>
       <c r="G46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H46" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>8</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C47" t="s">
         <v>29</v>
@@ -2455,24 +2324,24 @@
         <v>25</v>
       </c>
       <c r="E47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F47" t="s">
         <v>16</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H47" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C48" t="s">
         <v>29</v>
@@ -2481,24 +2350,24 @@
         <v>25</v>
       </c>
       <c r="E48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F48" t="s">
         <v>16</v>
       </c>
       <c r="G48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H48" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s">
         <v>29</v>
@@ -2507,24 +2376,24 @@
         <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F49" t="s">
         <v>16</v>
       </c>
       <c r="G49" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H49" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C50" t="s">
         <v>29</v>
@@ -2533,24 +2402,24 @@
         <v>25</v>
       </c>
       <c r="E50" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
       </c>
       <c r="G50" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H50" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C51" t="s">
         <v>29</v>
@@ -2559,24 +2428,24 @@
         <v>25</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F51" t="s">
         <v>16</v>
       </c>
       <c r="G51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H51" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C52" t="s">
         <v>29</v>
@@ -2585,24 +2454,24 @@
         <v>25</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F52" t="s">
         <v>16</v>
       </c>
       <c r="G52" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H52" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C53" t="s">
         <v>29</v>
@@ -2611,24 +2480,24 @@
         <v>25</v>
       </c>
       <c r="E53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
       </c>
       <c r="G53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H53" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C54" t="s">
         <v>29</v>
@@ -2637,24 +2506,24 @@
         <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H54" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C55" t="s">
         <v>29</v>
@@ -2663,24 +2532,24 @@
         <v>25</v>
       </c>
       <c r="E55" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F55" t="s">
         <v>16</v>
       </c>
       <c r="G55" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H55" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C56" t="s">
         <v>29</v>
@@ -2689,24 +2558,24 @@
         <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F56" t="s">
         <v>16</v>
       </c>
       <c r="G56" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H56" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C57" t="s">
         <v>29</v>
@@ -2715,19 +2584,27 @@
         <v>25</v>
       </c>
       <c r="E57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F57" t="s">
         <v>16</v>
       </c>
       <c r="G57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H57" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E57" xr:uid="{139CEA84-C4B4-485C-BA53-F6D94D33C0C8}">
+      <formula1>"OLD,NEW"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I57" xr:uid="{4B2B8E1E-CD53-4FE9-BC14-C492A9A96271}">
+      <formula1>"TRUE,"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -2769,7 +2646,7 @@
           <x14:formula1>
             <xm:f>Data!$M:$M</xm:f>
           </x14:formula1>
-          <xm:sqref>B1 B12:B16 B18:B25 B28:B32 B44:B1048576</xm:sqref>
+          <xm:sqref>B44:B1048576 B12:B16 B18:B25 B28:B32</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{787C674B-413B-4ABD-9C01-B0BC19335961}">
           <x14:formula1>
@@ -2785,30 +2662,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28D39F0B-52EC-49B9-8603-082D0C8B0935}">
-  <dimension ref="A1:Q47"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M47"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="2" style="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="2" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.140625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="1.28515625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="10.140625" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="11" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -2833,14 +2706,8 @@
       <c r="M1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -2866,14 +2733,8 @@
         <f>_xlfn.CONCAT(Table39[[#This Row],[Tables]], " &gt; ", Table39[[#This Row],[Columns]])</f>
         <v>albums &gt; album_artist</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2899,11 +2760,8 @@
         <f>_xlfn.CONCAT(Table39[[#This Row],[Tables]], " &gt; ", Table39[[#This Row],[Columns]])</f>
         <v>albums &gt; album_id</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2930,7 +2788,7 @@
         <v>albums &gt; album_name</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E5" s="1" t="s">
         <v>28</v>
       </c>
@@ -2951,7 +2809,7 @@
         <v>albums &gt; album_type</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
@@ -2972,7 +2830,7 @@
         <v>albums &gt; release_date</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I7" s="1" t="s">
         <v>35</v>
       </c>
@@ -2987,9 +2845,9 @@
         <v>albums_links &gt; album_id</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="I8" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>44</v>
@@ -3002,7 +2860,7 @@
         <v>artists &gt; albums_count</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K9" s="1" t="s">
         <v>44</v>
       </c>
@@ -3014,7 +2872,7 @@
         <v>artists &gt; artist_id</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K10" s="1" t="s">
         <v>44</v>
       </c>
@@ -3026,7 +2884,7 @@
         <v>artists &gt; artist_name</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K11" s="1" t="s">
         <v>44</v>
       </c>
@@ -3038,7 +2896,7 @@
         <v>artists &gt; other_names</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K12" s="1" t="s">
         <v>44</v>
       </c>
@@ -3050,7 +2908,7 @@
         <v>artists &gt; songs_count</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K13" s="1" t="s">
         <v>49</v>
       </c>
@@ -3062,7 +2920,7 @@
         <v>artists_links &gt; artist_id</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K14" s="1" t="s">
         <v>55</v>
       </c>
@@ -3074,7 +2932,7 @@
         <v>genres &gt; description</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K15" s="1" t="s">
         <v>55</v>
       </c>
@@ -3086,7 +2944,7 @@
         <v>genres &gt; genre_name</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="K16" s="1" t="s">
         <v>55</v>
       </c>
@@ -3098,7 +2956,7 @@
         <v>genres &gt; id</v>
       </c>
     </row>
-    <row r="17" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K17" s="1" t="s">
         <v>55</v>
       </c>
@@ -3110,7 +2968,7 @@
         <v>genres &gt; songs_count</v>
       </c>
     </row>
-    <row r="18" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K18" s="1" t="s">
         <v>57</v>
       </c>
@@ -3122,7 +2980,7 @@
         <v>music_groups &gt; group_name</v>
       </c>
     </row>
-    <row r="19" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K19" s="1" t="s">
         <v>57</v>
       </c>
@@ -3134,7 +2992,7 @@
         <v>music_groups &gt; id</v>
       </c>
     </row>
-    <row r="20" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="20" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K20" s="1" t="s">
         <v>57</v>
       </c>
@@ -3146,7 +3004,7 @@
         <v>music_groups &gt; pending_count</v>
       </c>
     </row>
-    <row r="21" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K21" s="1" t="s">
         <v>57</v>
       </c>
@@ -3158,7 +3016,7 @@
         <v>music_groups &gt; songs_count</v>
       </c>
     </row>
-    <row r="22" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K22" s="1" t="s">
         <v>58</v>
       </c>
@@ -3170,7 +3028,7 @@
         <v>pending_songs &gt; feat_artist</v>
       </c>
     </row>
-    <row r="23" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="23" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K23" s="1" t="s">
         <v>58</v>
       </c>
@@ -3182,7 +3040,7 @@
         <v>pending_songs &gt; is_added</v>
       </c>
     </row>
-    <row r="24" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K24" s="1" t="s">
         <v>58</v>
       </c>
@@ -3194,7 +3052,7 @@
         <v>pending_songs &gt; main_artist</v>
       </c>
     </row>
-    <row r="25" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K25" s="1" t="s">
         <v>58</v>
       </c>
@@ -3206,7 +3064,7 @@
         <v>pending_songs &gt; new_artist</v>
       </c>
     </row>
-    <row r="26" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="26" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K26" s="1" t="s">
         <v>58</v>
       </c>
@@ -3218,7 +3076,7 @@
         <v>pending_songs &gt; pending_id</v>
       </c>
     </row>
-    <row r="27" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K27" s="1" t="s">
         <v>58</v>
       </c>
@@ -3230,7 +3088,7 @@
         <v>pending_songs &gt; song_title</v>
       </c>
     </row>
-    <row r="28" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K28" s="1" t="s">
         <v>58</v>
       </c>
@@ -3242,7 +3100,7 @@
         <v>pending_songs &gt; to_group</v>
       </c>
     </row>
-    <row r="29" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="29" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K29" s="1" t="s">
         <v>65</v>
       </c>
@@ -3254,7 +3112,7 @@
         <v>playlists &gt; notes</v>
       </c>
     </row>
-    <row r="30" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K30" s="1" t="s">
         <v>65</v>
       </c>
@@ -3266,7 +3124,7 @@
         <v>playlists &gt; playlist_id</v>
       </c>
     </row>
-    <row r="31" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="31" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K31" s="1" t="s">
         <v>65</v>
       </c>
@@ -3278,7 +3136,7 @@
         <v>playlists &gt; playlist_image</v>
       </c>
     </row>
-    <row r="32" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="32" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K32" s="1" t="s">
         <v>65</v>
       </c>
@@ -3290,7 +3148,7 @@
         <v>playlists &gt; playlist_link</v>
       </c>
     </row>
-    <row r="33" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K33" s="1" t="s">
         <v>65</v>
       </c>
@@ -3302,7 +3160,7 @@
         <v>playlists &gt; playlist_name</v>
       </c>
     </row>
-    <row r="34" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K34" s="1" t="s">
         <v>65</v>
       </c>
@@ -3314,7 +3172,7 @@
         <v>playlists &gt; songs_count</v>
       </c>
     </row>
-    <row r="35" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K35" s="1" t="s">
         <v>65</v>
       </c>
@@ -3326,7 +3184,7 @@
         <v>playlists &gt; spotify_count</v>
       </c>
     </row>
-    <row r="36" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K36" s="1" t="s">
         <v>71</v>
       </c>
@@ -3338,7 +3196,7 @@
         <v>song_playlist_relations &gt; id</v>
       </c>
     </row>
-    <row r="37" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K37" s="1" t="s">
         <v>71</v>
       </c>
@@ -3350,7 +3208,7 @@
         <v>song_playlist_relations &gt; playlist_id</v>
       </c>
     </row>
-    <row r="38" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K38" s="1" t="s">
         <v>71</v>
       </c>
@@ -3362,7 +3220,7 @@
         <v>song_playlist_relations &gt; song_id</v>
       </c>
     </row>
-    <row r="39" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K39" s="1" t="s">
         <v>72</v>
       </c>
@@ -3374,7 +3232,7 @@
         <v>songs &gt; album_id</v>
       </c>
     </row>
-    <row r="40" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K40" s="1" t="s">
         <v>72</v>
       </c>
@@ -3386,7 +3244,7 @@
         <v>songs &gt; feat_artist</v>
       </c>
     </row>
-    <row r="41" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K41" s="1" t="s">
         <v>72</v>
       </c>
@@ -3398,7 +3256,7 @@
         <v>songs &gt; genre</v>
       </c>
     </row>
-    <row r="42" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K42" s="1" t="s">
         <v>72</v>
       </c>
@@ -3410,7 +3268,7 @@
         <v>songs &gt; group</v>
       </c>
     </row>
-    <row r="43" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K43" s="1" t="s">
         <v>72</v>
       </c>
@@ -3422,7 +3280,7 @@
         <v>songs &gt; main_artist</v>
       </c>
     </row>
-    <row r="44" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K44" s="1" t="s">
         <v>72</v>
       </c>
@@ -3434,7 +3292,7 @@
         <v>songs &gt; song_id</v>
       </c>
     </row>
-    <row r="45" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K45" s="1" t="s">
         <v>72</v>
       </c>
@@ -3446,7 +3304,7 @@
         <v>songs &gt; song_title</v>
       </c>
     </row>
-    <row r="46" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K46" s="1" t="s">
         <v>72</v>
       </c>
@@ -3458,7 +3316,7 @@
         <v>songs &gt; song_year</v>
       </c>
     </row>
-    <row r="47" spans="11:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="11:13" x14ac:dyDescent="0.3">
       <c r="K47" s="1" t="s">
         <v>72</v>
       </c>
@@ -3472,15 +3330,13 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="8">
+  <tableParts count="6">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
-    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>